--- a/utils/insumos/regras_operadora.xlsx
+++ b/utils/insumos/regras_operadora.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hapvida-my.sharepoint.com/personal/anderson_dossantos_hapvida_com_br/Documents/5 Estrelas/INSUMOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.dossantos\Desktop\dev\5 Estrelas\utils\insumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_3135441469BDFA87A5BE078EBA3C0371A7927FA0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DFE74BD-5A3F-43EB-A515-9437B239E797}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63016357-119B-4C83-A622-565C94A5EA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3084" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3091" uniqueCount="899">
   <si>
     <t>OPERADORA</t>
   </si>
@@ -2712,6 +2712,12 @@
   </si>
   <si>
     <t>Valor da coluna deve estar preenchido.</t>
+  </si>
+  <si>
+    <t>AMBULANCIA</t>
+  </si>
+  <si>
+    <t>ajustar ambulancia para operadora hapvida</t>
   </si>
 </sst>
 </file>
@@ -3029,7 +3035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -14397,6 +14403,32 @@
       </c>
       <c r="N429" t="s">
         <v>885</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>870</v>
+      </c>
+      <c r="B430" t="s">
+        <v>19</v>
+      </c>
+      <c r="C430" t="s">
+        <v>16</v>
+      </c>
+      <c r="D430" t="s">
+        <v>26</v>
+      </c>
+      <c r="E430" t="s">
+        <v>897</v>
+      </c>
+      <c r="L430">
+        <v>429</v>
+      </c>
+      <c r="M430" t="s">
+        <v>19</v>
+      </c>
+      <c r="N430" t="s">
+        <v>898</v>
       </c>
     </row>
   </sheetData>
